--- a/Plannings 2026 S22.xlsx
+++ b/Plannings 2026 S22.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B78CE403-7A3C-475B-B7DB-0642BE414435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B78CE403-7A3C-475B-B7DB-0642BE414435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D55EF36-1C90-421C-BD98-9257444CB595}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -913,7 +914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,19 +949,7 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -968,9 +957,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -982,14 +968,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -998,28 +977,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1038,7 +996,7 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1054,7 +1012,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1073,7 +1031,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1115,7 +1073,49 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7286,152 +7286,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="12" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="47" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="19"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="56" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="23"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="23"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -7446,96 +7446,95 @@
       <c r="G10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="26"/>
+      <c r="A11" s="65"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="54" t="s">
         <v>141</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="70" t="s">
+      <c r="G11" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="H11" s="25"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="45" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="53" t="s">
+      <c r="F12" s="17"/>
+      <c r="G12" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="23"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22" t="s">
+      <c r="A14" s="66"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="23"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="39" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="25"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="1"/>
       <c r="C17" s="2" t="s">
         <v>15</v>
@@ -7544,47 +7543,47 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="25"/>
+      <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22" t="s">
+      <c r="A18" s="66"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="19"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="40" t="s">
         <v>36</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -7594,10 +7593,10 @@
         <v>38</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="25"/>
+      <c r="H20" s="19"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
@@ -7606,10 +7605,10 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="25"/>
+      <c r="H21" s="19"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
@@ -7618,224 +7617,224 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="25"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18" t="s">
+      <c r="B23" s="13"/>
+      <c r="C23" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18" t="s">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18" t="s">
+      <c r="F23" s="14"/>
+      <c r="G23" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="19"/>
+      <c r="H23" s="15"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22" t="s">
+      <c r="A24" s="66"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22" t="s">
+      <c r="D24" s="17"/>
+      <c r="E24" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="17"/>
+      <c r="G24" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="23"/>
+      <c r="H24" s="18"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="47" t="s">
+      <c r="E25" s="14"/>
+      <c r="F25" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="H25" s="19"/>
+      <c r="H25" s="15"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="48" t="s">
+      <c r="A26" s="65"/>
+      <c r="B26" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="33" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="48" t="s">
+      <c r="F26" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="G26" s="52" t="s">
+      <c r="G26" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="25"/>
+      <c r="H26" s="19"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
+      <c r="A27" s="65"/>
       <c r="B27" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="34" t="s">
         <v>44</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="52"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="19"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="33" t="s">
         <v>54</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="52" t="s">
+      <c r="F28" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="52"/>
-      <c r="H28" s="25"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="19"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="49" t="s">
+      <c r="A29" s="65"/>
+      <c r="B29" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="34" t="s">
         <v>44</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="25"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="48" t="s">
+      <c r="A30" s="65"/>
+      <c r="B30" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="33" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="25"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="19"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="49" t="s">
+      <c r="A31" s="65"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="25"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="19"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48" t="s">
+      <c r="A32" s="65"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33" t="s">
         <v>60</v>
       </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="25"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="47" t="s">
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="19"/>
+      <c r="H33" s="15"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="20"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="56" t="s">
+      <c r="A34" s="66"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="23"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18" t="s">
+      <c r="E35" s="14"/>
+      <c r="F35" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G35" s="18"/>
-      <c r="H35" s="58" t="s">
+      <c r="G35" s="14"/>
+      <c r="H35" s="43" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
+      <c r="A36" s="65"/>
       <c r="B36" s="1" t="s">
         <v>64</v>
       </c>
@@ -7848,48 +7847,48 @@
         <v>66</v>
       </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="59" t="s">
+      <c r="H36" s="44" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="49" t="s">
+      <c r="A37" s="65"/>
+      <c r="B37" s="34" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="49" t="s">
+      <c r="D37" s="34" t="s">
         <v>68</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="34" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="28" t="s">
+      <c r="H37" s="20" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="48" t="s">
+      <c r="A38" s="65"/>
+      <c r="B38" s="33" t="s">
         <v>69</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="33" t="s">
         <v>70</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="48" t="s">
+      <c r="F38" s="33" t="s">
         <v>69</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="25" t="s">
+      <c r="H38" s="19" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
+      <c r="A39" s="65"/>
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
@@ -7898,12 +7897,12 @@
         <v>15</v>
       </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="48"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="25"/>
+      <c r="H39" s="19"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
+      <c r="A40" s="65"/>
       <c r="B40" s="1" t="s">
         <v>16</v>
       </c>
@@ -7912,512 +7911,510 @@
         <v>72</v>
       </c>
       <c r="E40" s="1"/>
-      <c r="F40" s="48"/>
+      <c r="F40" s="33"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="25"/>
+      <c r="H40" s="19"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="26"/>
+      <c r="A41" s="65"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="49" t="s">
+      <c r="D41" s="34" t="s">
         <v>68</v>
       </c>
       <c r="E41" s="1"/>
-      <c r="F41" s="48"/>
+      <c r="F41" s="33"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="25"/>
+      <c r="H41" s="19"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="20"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="56" t="s">
+      <c r="A42" s="66"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="23"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="18"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="19"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="15"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="20"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22" t="s">
+      <c r="A44" s="66"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="23"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="18"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="30"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="32"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="60"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="19" t="s">
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="23" t="s">
+      <c r="A47" s="66"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="18" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="58" t="s">
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="43" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
+      <c r="A49" s="65"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="59" t="s">
+      <c r="H49" s="44" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="24"/>
+      <c r="A50" s="65"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="66" t="s">
+      <c r="H50" s="51" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="20"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="68" t="s">
+      <c r="A51" s="66"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="53" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="47" t="s">
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="39" t="s">
+      <c r="E52" s="14"/>
+      <c r="F52" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G52" s="18"/>
-      <c r="H52" s="19"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="15"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="24"/>
+      <c r="A53" s="65"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="48" t="s">
+      <c r="D53" s="33" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="1"/>
-      <c r="F53" s="40" t="s">
+      <c r="F53" s="25" t="s">
         <v>82</v>
       </c>
       <c r="G53" s="1"/>
-      <c r="H53" s="25"/>
+      <c r="H53" s="19"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="24"/>
+      <c r="A54" s="65"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="48"/>
+      <c r="D54" s="33"/>
       <c r="E54" s="1"/>
       <c r="F54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="1"/>
-      <c r="H54" s="25"/>
+      <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="22" t="s">
+      <c r="A55" s="66"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="G55" s="22"/>
-      <c r="H55" s="23"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="18"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="33" t="s">
+      <c r="A56" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="36"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="63"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="60" t="s">
+      <c r="B57" s="13"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="H57" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
+      <c r="A58" s="65"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="H58" s="25" t="s">
+      <c r="H58" s="19" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
+      <c r="A59" s="65"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="62" t="s">
+      <c r="G59" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="64" t="s">
+      <c r="H59" s="49" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
+      <c r="A60" s="65"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="61" t="s">
+      <c r="G60" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="H60" s="59" t="s">
+      <c r="H60" s="44" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
+      <c r="A61" s="65"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="28" t="s">
+      <c r="G61" s="46"/>
+      <c r="H61" s="20" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
+      <c r="A62" s="65"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="25" t="s">
+      <c r="G62" s="46"/>
+      <c r="H62" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
+      <c r="A63" s="65"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="64" t="s">
+      <c r="G63" s="46"/>
+      <c r="H63" s="49" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
+      <c r="A64" s="65"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="59" t="s">
+      <c r="G64" s="46"/>
+      <c r="H64" s="44" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
+      <c r="A65" s="65"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="66" t="s">
+      <c r="G65" s="46"/>
+      <c r="H65" s="51" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="20"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="63"/>
-      <c r="H66" s="68" t="s">
+      <c r="A66" s="66"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="53" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="46" t="s">
+      <c r="B67" s="13"/>
+      <c r="C67" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="D67" s="46" t="s">
+      <c r="D67" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="19"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="15"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="20"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="45" t="s">
+      <c r="A68" s="66"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D68" s="45" t="s">
+      <c r="D68" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="23"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="18"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C69" s="47" t="s">
+      <c r="C69" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="19"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="15"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="24"/>
+      <c r="A70" s="65"/>
       <c r="B70" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C70" s="48" t="s">
+      <c r="C70" s="33" t="s">
         <v>69</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="25"/>
+      <c r="H70" s="19"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="42" t="s">
+      <c r="A71" s="65"/>
+      <c r="C71" s="27" t="s">
         <v>93</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-      <c r="H71" s="25"/>
+      <c r="H71" s="19"/>
     </row>
     <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="20"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="45" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="23"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="18"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="39" t="s">
+      <c r="B73" s="13"/>
+      <c r="C73" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="47" t="s">
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="18"/>
-      <c r="H73" s="58" t="s">
+      <c r="G73" s="14"/>
+      <c r="H73" s="43" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
+      <c r="A74" s="65"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="40" t="s">
+      <c r="C74" s="25" t="s">
         <v>82</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="48" t="s">
+      <c r="F74" s="33" t="s">
         <v>69</v>
       </c>
       <c r="G74" s="1"/>
-      <c r="H74" s="59" t="s">
+      <c r="H74" s="44" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="24"/>
+      <c r="A75" s="65"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="49" t="s">
+      <c r="C75" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="48"/>
+      <c r="F75" s="33"/>
       <c r="G75" s="1"/>
-      <c r="H75" s="59"/>
+      <c r="H75" s="44"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="20"/>
-      <c r="B76" s="22"/>
-      <c r="C76" s="56" t="s">
+      <c r="A76" s="66"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="D76" s="22"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="56"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="65"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="50"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="18" t="s">
+      <c r="E77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F77" s="18" t="s">
+      <c r="F77" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G77" s="18"/>
-      <c r="H77" s="19" t="s">
+      <c r="G77" s="14"/>
+      <c r="H77" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="24"/>
+      <c r="A78" s="65"/>
       <c r="B78" s="1" t="s">
         <v>101</v>
       </c>
@@ -8434,48 +8431,47 @@
         <v>105</v>
       </c>
       <c r="G78" s="1"/>
-      <c r="H78" s="25" t="s">
+      <c r="H78" s="19" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="41" t="s">
+      <c r="A79" s="65"/>
+      <c r="C79" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D79" s="41" t="s">
+      <c r="D79" s="26" t="s">
         <v>30</v>
       </c>
       <c r="E79" s="1"/>
-      <c r="F79" s="41" t="s">
+      <c r="F79" s="26" t="s">
         <v>30</v>
       </c>
       <c r="G79" s="1"/>
-      <c r="H79" s="66" t="s">
+      <c r="H79" s="51" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
+      <c r="A80" s="65"/>
       <c r="B80" s="1"/>
-      <c r="C80" s="40" t="s">
+      <c r="C80" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="D80" s="40" t="s">
+      <c r="D80" s="25" t="s">
         <v>107</v>
       </c>
       <c r="E80" s="1"/>
-      <c r="F80" s="40" t="s">
+      <c r="F80" s="25" t="s">
         <v>108</v>
       </c>
       <c r="G80" s="1"/>
-      <c r="H80" s="67" t="s">
+      <c r="H80" s="52" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
+      <c r="A81" s="65"/>
       <c r="B81" s="1"/>
       <c r="C81" s="2" t="s">
         <v>15</v>
@@ -8488,10 +8484,10 @@
         <v>15</v>
       </c>
       <c r="G81" s="1"/>
-      <c r="H81" s="67"/>
+      <c r="H81" s="52"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
+      <c r="A82" s="65"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
         <v>110</v>
@@ -8504,34 +8500,34 @@
         <v>112</v>
       </c>
       <c r="G82" s="1"/>
-      <c r="H82" s="67"/>
+      <c r="H82" s="52"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="24"/>
+      <c r="A83" s="65"/>
       <c r="B83" s="1"/>
-      <c r="C83" s="41" t="s">
+      <c r="C83" s="26" t="s">
         <v>30</v>
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
-      <c r="H83" s="67"/>
+      <c r="H83" s="52"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="24"/>
+      <c r="A84" s="65"/>
       <c r="B84" s="1"/>
-      <c r="C84" s="40" t="s">
+      <c r="C84" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-      <c r="H84" s="67"/>
+      <c r="H84" s="52"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="24"/>
+      <c r="A85" s="65"/>
       <c r="B85" s="1"/>
       <c r="C85" s="2" t="s">
         <v>15</v>
@@ -8540,38 +8536,38 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-      <c r="H85" s="67"/>
+      <c r="H85" s="52"/>
     </row>
     <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="20"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="22" t="s">
+      <c r="A86" s="66"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D86" s="22"/>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22"/>
-      <c r="G86" s="22"/>
-      <c r="H86" s="68"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="17"/>
+      <c r="G86" s="17"/>
+      <c r="H86" s="53"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18" t="s">
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H87" s="19"/>
+      <c r="H87" s="15"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="24"/>
+      <c r="A88" s="65"/>
       <c r="B88" s="1" t="s">
         <v>115</v>
       </c>
@@ -8582,39 +8578,39 @@
       <c r="G88" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H88" s="25"/>
+      <c r="H88" s="19"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="24"/>
-      <c r="B89" s="42" t="s">
+      <c r="A89" s="65"/>
+      <c r="B89" s="27" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
-      <c r="G89" s="62" t="s">
+      <c r="G89" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="H89" s="25"/>
+      <c r="H89" s="19"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="24"/>
-      <c r="B90" s="43" t="s">
+      <c r="A90" s="65"/>
+      <c r="B90" s="28" t="s">
         <v>94</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="61" t="s">
+      <c r="G90" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="H90" s="25"/>
+      <c r="H90" s="19"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
-      <c r="B91" s="44"/>
+      <c r="A91" s="65"/>
+      <c r="B91" s="29"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -8622,168 +8618,168 @@
       <c r="G91" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H91" s="25"/>
+      <c r="H91" s="19"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22" t="s">
+      <c r="A92" s="66"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="H92" s="23"/>
+      <c r="H92" s="18"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="39" t="s">
+      <c r="B93" s="13"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
-      <c r="H93" s="19"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="15"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
+      <c r="A94" s="65"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="40" t="s">
+      <c r="D94" s="25" t="s">
         <v>107</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-      <c r="H94" s="25"/>
+      <c r="H94" s="19"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
+      <c r="A95" s="65"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="34" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-      <c r="H95" s="25"/>
+      <c r="H95" s="19"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22" t="s">
+      <c r="A96" s="66"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="23"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="18"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="47" t="s">
+      <c r="B97" s="13"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H97" s="71"/>
+      <c r="H97" s="56"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="24"/>
+      <c r="A98" s="65"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="48" t="s">
+      <c r="G98" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H98" s="25"/>
+      <c r="H98" s="19"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
+      <c r="A99" s="65"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="49" t="s">
+      <c r="G99" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H99" s="25"/>
+      <c r="H99" s="19"/>
     </row>
     <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="20"/>
-      <c r="B100" s="22"/>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22"/>
-      <c r="E100" s="22"/>
-      <c r="F100" s="22"/>
-      <c r="G100" s="56" t="s">
+      <c r="A100" s="66"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="H100" s="23"/>
+      <c r="H100" s="18"/>
     </row>
     <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="29" t="s">
+      <c r="A101" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B101" s="30"/>
-      <c r="C101" s="31"/>
-      <c r="D101" s="31"/>
-      <c r="E101" s="31"/>
-      <c r="F101" s="31"/>
-      <c r="G101" s="31"/>
-      <c r="H101" s="32"/>
+      <c r="B101" s="58"/>
+      <c r="C101" s="59"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="59"/>
+      <c r="F101" s="59"/>
+      <c r="G101" s="59"/>
+      <c r="H101" s="60"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="46" t="s">
+      <c r="B102" s="13"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E102" s="18"/>
-      <c r="F102" s="39" t="s">
+      <c r="E102" s="14"/>
+      <c r="F102" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="G102" s="60" t="s">
+      <c r="G102" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="H102" s="19"/>
+      <c r="H102" s="15"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="24"/>
+      <c r="A103" s="65"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
-      <c r="D103" s="43" t="s">
+      <c r="D103" s="28" t="s">
         <v>97</v>
       </c>
       <c r="E103" s="1"/>
-      <c r="F103" s="40" t="s">
+      <c r="F103" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="G103" s="61" t="s">
+      <c r="G103" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="H103" s="25"/>
+      <c r="H103" s="19"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="24"/>
+      <c r="A104" s="65"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="2" t="s">
@@ -8793,113 +8789,127 @@
       <c r="F104" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G104" s="61"/>
-      <c r="H104" s="25"/>
+      <c r="G104" s="46"/>
+      <c r="H104" s="19"/>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="20"/>
-      <c r="B105" s="22"/>
-      <c r="C105" s="22"/>
-      <c r="D105" s="22" t="s">
+      <c r="A105" s="66"/>
+      <c r="B105" s="17"/>
+      <c r="C105" s="17"/>
+      <c r="D105" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="E105" s="22"/>
-      <c r="F105" s="22" t="s">
+      <c r="E105" s="17"/>
+      <c r="F105" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G105" s="63"/>
-      <c r="H105" s="23"/>
+      <c r="G105" s="48"/>
+      <c r="H105" s="18"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="B106" s="17"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="47" t="s">
+      <c r="B106" s="13"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E106" s="18"/>
-      <c r="F106" s="18"/>
-      <c r="G106" s="47" t="s">
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="H106" s="19"/>
+      <c r="H106" s="15"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="24"/>
+      <c r="A107" s="65"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
-      <c r="D107" s="48" t="s">
+      <c r="D107" s="33" t="s">
         <v>49</v>
       </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="48" t="s">
+      <c r="G107" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="H107" s="25"/>
+      <c r="H107" s="19"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="24"/>
+      <c r="A108" s="65"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
-      <c r="D108" s="48"/>
+      <c r="D108" s="33"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="49" t="s">
+      <c r="G108" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H108" s="25"/>
-      <c r="K108" s="38"/>
+      <c r="H108" s="19"/>
+      <c r="K108" s="23"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="24"/>
+      <c r="A109" s="65"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
-      <c r="D109" s="48"/>
+      <c r="D109" s="33"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
-      <c r="G109" s="48" t="s">
+      <c r="G109" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="H109" s="25"/>
+      <c r="H109" s="19"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="24"/>
+      <c r="A110" s="65"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
-      <c r="D110" s="48"/>
+      <c r="D110" s="33"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
-      <c r="G110" s="62" t="s">
+      <c r="G110" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="H110" s="25"/>
+      <c r="H110" s="19"/>
     </row>
     <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="20"/>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="22"/>
-      <c r="F111" s="22"/>
-      <c r="G111" s="63" t="s">
+      <c r="A111" s="66"/>
+      <c r="B111" s="17"/>
+      <c r="C111" s="17"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="17"/>
+      <c r="F111" s="17"/>
+      <c r="G111" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="H111" s="23"/>
+      <c r="H111" s="18"/>
     </row>
     <row r="112" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="37"/>
-      <c r="C112" s="37"/>
-      <c r="D112" s="37"/>
-      <c r="E112" s="37"/>
-      <c r="F112" s="37"/>
-      <c r="G112" s="37"/>
-      <c r="H112" s="37"/>
+      <c r="B112" s="57"/>
+      <c r="C112" s="57"/>
+      <c r="D112" s="57"/>
+      <c r="E112" s="57"/>
+      <c r="F112" s="57"/>
+      <c r="G112" s="57"/>
+      <c r="H112" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A57:A66"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A32"/>
     <mergeCell ref="B112:H112"/>
     <mergeCell ref="B101:H101"/>
     <mergeCell ref="B45:H45"/>
@@ -8916,20 +8926,6 @@
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A51"/>
     <mergeCell ref="A52:A55"/>
-    <mergeCell ref="A57:A66"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A32"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8948,20 +8944,20 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -9679,15 +9675,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
@@ -9698,14 +9685,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5D686E-33C9-4E8F-99B7-7F980CD75D18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5D686E-33C9-4E8F-99B7-7F980CD75D18}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47060B1A-696C-4816-A1CB-39D110D3C65C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E78225C-60DD-40CE-981E-C126BF3AF24C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E78225C-60DD-40CE-981E-C126BF3AF24C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47060B1A-696C-4816-A1CB-39D110D3C65C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>